--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,6 +1853,5157 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133748644</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>638170</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7034063</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133751145</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>638754</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033961</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133747890</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92338</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>638059</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7034046</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133748002</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>638084</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7034064</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133745580</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>637989</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7034113</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133747219</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>638061</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7034028</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133754875</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92338</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>638759</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7033860</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133754154</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92217</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>658</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>638798</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7033915</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133750092</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92217</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>638348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7033866</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133749740</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>638232</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7034015</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133754254</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>638764</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7033933</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133747740</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>638064</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7034062</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133745623</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>638018</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7034124</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133749592</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>638226</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7034023</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133752723</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>639153</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7033913</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133748271</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>638131</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7034032</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133745777</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92217</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>638007</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7034104</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133747269</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>638060</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7034027</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133755234</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>638761</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7033856</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133750539</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>638536</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7033920</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133751356</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>638872</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7034031</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133751033</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98001</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>638655</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7033936</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133748499</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>638163</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7034015</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133754937</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>638759</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7033864</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133750904</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>638620</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7033897</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133748793</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>638181</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7034067</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133752639</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>639103</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7033979</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133749803</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>638278</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7033979</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133754117</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>638808</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7033918</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133753992</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>638860</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7033902</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133747733</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92614</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>898</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>638052</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7034053</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133753051</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>638997</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7033854</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133752438</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80466</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>638928</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7033996</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133752659</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>639104</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7033978</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133752847</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>639087</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7033883</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>133747834</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92217</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>658</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>638050</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7034042</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>133754841</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92378</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>638763</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7033857</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>133755227</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>638752</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7033861</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133748929</v>
+      </c>
+      <c r="B51" t="n">
+        <v>89300</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>510</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>638198</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7034077</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133748447</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>638162</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7034014</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133745736</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>637993</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7034094</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133752568</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>639034</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7034020</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133752413</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>638923</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7034016</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133750078</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>638351</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7033867</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133751279</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>638805</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7034008</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133752304</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>638897</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7034043</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133752701</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>639153</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7033912</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133749947</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>638326</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7033938</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133752378</v>
+      </c>
+      <c r="B61" t="n">
+        <v>89300</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>510</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>638902</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7034025</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133747965</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>638071</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7034053</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133750259</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>638396</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7033893</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133750648</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>638588</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7033862</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133754273</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92378</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>638763</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7033932</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133745580</v>
+        <v>133754875</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,34 +2255,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637989</v>
+        <v>638759</v>
       </c>
       <c r="R17" t="n">
-        <v>7034113</v>
+        <v>7033860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133747219</v>
+        <v>133754154</v>
       </c>
       <c r="B18" t="n">
-        <v>80438</v>
+        <v>92217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638061</v>
+        <v>638798</v>
       </c>
       <c r="R18" t="n">
-        <v>7034028</v>
+        <v>7033915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133754875</v>
+        <v>133745580</v>
       </c>
       <c r="B19" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,34 +2449,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638759</v>
+        <v>637989</v>
       </c>
       <c r="R19" t="n">
-        <v>7033860</v>
+        <v>7034113</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133754154</v>
+        <v>133747219</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>80438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638798</v>
+        <v>638061</v>
       </c>
       <c r="R20" t="n">
-        <v>7033915</v>
+        <v>7034028</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133750092</v>
+        <v>133749740</v>
       </c>
       <c r="B21" t="n">
-        <v>92217</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638348</v>
+        <v>638232</v>
       </c>
       <c r="R21" t="n">
-        <v>7033866</v>
+        <v>7034015</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133749740</v>
+        <v>133750092</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>92217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638232</v>
+        <v>638348</v>
       </c>
       <c r="R22" t="n">
-        <v>7034015</v>
+        <v>7033866</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3020,45 +3020,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133745623</v>
+        <v>133749592</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638018</v>
+        <v>638226</v>
       </c>
       <c r="R25" t="n">
-        <v>7034124</v>
+        <v>7034023</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,50 +3122,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133749592</v>
+        <v>133745623</v>
       </c>
       <c r="B26" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638226</v>
+        <v>638018</v>
       </c>
       <c r="R26" t="n">
-        <v>7034023</v>
+        <v>7034124</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133751033</v>
+        <v>133748499</v>
       </c>
       <c r="B34" t="n">
-        <v>98001</v>
+        <v>91881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638655</v>
+        <v>638163</v>
       </c>
       <c r="R34" t="n">
-        <v>7033936</v>
+        <v>7034015</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133748499</v>
+        <v>133751033</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>98001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638163</v>
+        <v>638655</v>
       </c>
       <c r="R35" t="n">
-        <v>7034015</v>
+        <v>7033936</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133754937</v>
+        <v>133750904</v>
       </c>
       <c r="B36" t="n">
         <v>91918</v>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638759</v>
+        <v>638620</v>
       </c>
       <c r="R36" t="n">
-        <v>7033864</v>
+        <v>7033897</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133750904</v>
+        <v>133754937</v>
       </c>
       <c r="B37" t="n">
         <v>91918</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638620</v>
+        <v>638759</v>
       </c>
       <c r="R37" t="n">
-        <v>7033897</v>
+        <v>7033864</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B38" t="n">
         <v>79333</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R38" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B39" t="n">
         <v>79333</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R39" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133747834</v>
+        <v>133754841</v>
       </c>
       <c r="B48" t="n">
-        <v>92217</v>
+        <v>92378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638050</v>
+        <v>638763</v>
       </c>
       <c r="R48" t="n">
-        <v>7034042</v>
+        <v>7033857</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133754841</v>
+        <v>133755227</v>
       </c>
       <c r="B49" t="n">
-        <v>92378</v>
+        <v>91918</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638763</v>
+        <v>638752</v>
       </c>
       <c r="R49" t="n">
-        <v>7033857</v>
+        <v>7033861</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133755227</v>
+        <v>133747834</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638752</v>
+        <v>638050</v>
       </c>
       <c r="R50" t="n">
-        <v>7033861</v>
+        <v>7034042</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133750078</v>
+        <v>133752304</v>
       </c>
       <c r="B56" t="n">
         <v>79333</v>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638351</v>
+        <v>638897</v>
       </c>
       <c r="R56" t="n">
-        <v>7033867</v>
+        <v>7034043</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133751279</v>
+        <v>133750078</v>
       </c>
       <c r="B57" t="n">
         <v>79333</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638805</v>
+        <v>638351</v>
       </c>
       <c r="R57" t="n">
-        <v>7034008</v>
+        <v>7033867</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133752304</v>
+        <v>133751279</v>
       </c>
       <c r="B58" t="n">
         <v>79333</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638897</v>
+        <v>638805</v>
       </c>
       <c r="R58" t="n">
-        <v>7034043</v>
+        <v>7034008</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6619,32 +6619,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133747965</v>
+        <v>133750259</v>
       </c>
       <c r="B62" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638071</v>
+        <v>638396</v>
       </c>
       <c r="R62" t="n">
-        <v>7034053</v>
+        <v>7033893</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6716,32 +6716,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133750259</v>
+        <v>133747965</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638396</v>
+        <v>638071</v>
       </c>
       <c r="R63" t="n">
-        <v>7033893</v>
+        <v>7034053</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R14" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133747890</v>
+        <v>133748002</v>
       </c>
       <c r="B15" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638059</v>
+        <v>638084</v>
       </c>
       <c r="R15" t="n">
-        <v>7034046</v>
+        <v>7034064</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B16" t="n">
         <v>79333</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R16" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B38" t="n">
         <v>79333</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R38" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B39" t="n">
         <v>79333</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R39" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133752304</v>
+        <v>133750078</v>
       </c>
       <c r="B56" t="n">
         <v>79333</v>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638897</v>
+        <v>638351</v>
       </c>
       <c r="R56" t="n">
-        <v>7034043</v>
+        <v>7033867</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133750078</v>
+        <v>133751279</v>
       </c>
       <c r="B57" t="n">
         <v>79333</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638351</v>
+        <v>638805</v>
       </c>
       <c r="R57" t="n">
-        <v>7033867</v>
+        <v>7034008</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133751279</v>
+        <v>133752304</v>
       </c>
       <c r="B58" t="n">
         <v>79333</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638805</v>
+        <v>638897</v>
       </c>
       <c r="R58" t="n">
-        <v>7034008</v>
+        <v>7034043</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R59" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133749947</v>
+        <v>133752378</v>
       </c>
       <c r="B60" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638326</v>
+        <v>638902</v>
       </c>
       <c r="R60" t="n">
-        <v>7033938</v>
+        <v>7034025</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133752378</v>
+        <v>133752701</v>
       </c>
       <c r="B61" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638902</v>
+        <v>639153</v>
       </c>
       <c r="R61" t="n">
-        <v>7034025</v>
+        <v>7033912</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6619,7 +6619,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133750259</v>
+        <v>133750648</v>
       </c>
       <c r="B62" t="n">
         <v>79333</v>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638396</v>
+        <v>638588</v>
       </c>
       <c r="R62" t="n">
-        <v>7033893</v>
+        <v>7033862</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6716,32 +6716,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133747965</v>
+        <v>133754273</v>
       </c>
       <c r="B63" t="n">
-        <v>91881</v>
+        <v>92378</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638071</v>
+        <v>638763</v>
       </c>
       <c r="R63" t="n">
-        <v>7034053</v>
+        <v>7033932</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133750648</v>
+        <v>133750259</v>
       </c>
       <c r="B64" t="n">
         <v>79333</v>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638588</v>
+        <v>638396</v>
       </c>
       <c r="R64" t="n">
-        <v>7033862</v>
+        <v>7033893</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133754273</v>
+        <v>133747965</v>
       </c>
       <c r="B65" t="n">
-        <v>92378</v>
+        <v>91881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638763</v>
+        <v>638071</v>
       </c>
       <c r="R65" t="n">
-        <v>7033932</v>
+        <v>7034053</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1859,7 +1859,7 @@
         <v>133748644</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133747890</v>
+        <v>133751145</v>
       </c>
       <c r="B14" t="n">
-        <v>92338</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638059</v>
+        <v>638754</v>
       </c>
       <c r="R14" t="n">
-        <v>7034046</v>
+        <v>7033961</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2053,7 +2053,7 @@
         <v>133748002</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>92340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R16" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133754875</v>
+        <v>133747219</v>
       </c>
       <c r="B17" t="n">
-        <v>92338</v>
+        <v>80439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638759</v>
+        <v>638061</v>
       </c>
       <c r="R17" t="n">
-        <v>7033860</v>
+        <v>7034028</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133754154</v>
+        <v>133745580</v>
       </c>
       <c r="B18" t="n">
-        <v>92217</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,34 +2352,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638798</v>
+        <v>637989</v>
       </c>
       <c r="R18" t="n">
-        <v>7033915</v>
+        <v>7034113</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133745580</v>
+        <v>133754154</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>92219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,34 +2449,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637989</v>
+        <v>638798</v>
       </c>
       <c r="R19" t="n">
-        <v>7034113</v>
+        <v>7033915</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133747219</v>
+        <v>133754875</v>
       </c>
       <c r="B20" t="n">
-        <v>80438</v>
+        <v>92340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638061</v>
+        <v>638759</v>
       </c>
       <c r="R20" t="n">
-        <v>7034028</v>
+        <v>7033860</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2635,7 +2635,7 @@
         <v>133749740</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>133750092</v>
       </c>
       <c r="B22" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>133754254</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,45 +2923,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133747740</v>
+        <v>133749592</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638064</v>
+        <v>638226</v>
       </c>
       <c r="R24" t="n">
-        <v>7034062</v>
+        <v>7034023</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3020,50 +3025,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133749592</v>
+        <v>133747740</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>91920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638226</v>
+        <v>638064</v>
       </c>
       <c r="R25" t="n">
-        <v>7034023</v>
+        <v>7034062</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3125,7 +3125,7 @@
         <v>133745623</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R28" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3413,45 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133745777</v>
+        <v>133755234</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>91883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638007</v>
+        <v>638761</v>
       </c>
       <c r="R29" t="n">
-        <v>7034104</v>
+        <v>7033856</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,45 +3510,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133747269</v>
+        <v>133745777</v>
       </c>
       <c r="B30" t="n">
-        <v>80467</v>
+        <v>92219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638060</v>
+        <v>638007</v>
       </c>
       <c r="R30" t="n">
-        <v>7034027</v>
+        <v>7034104</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133755234</v>
+        <v>133747269</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638761</v>
+        <v>638060</v>
       </c>
       <c r="R31" t="n">
-        <v>7033856</v>
+        <v>7034027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133750539</v>
+        <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638536</v>
+        <v>638872</v>
       </c>
       <c r="R32" t="n">
-        <v>7033920</v>
+        <v>7034031</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3801,32 +3801,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133751356</v>
+        <v>133750539</v>
       </c>
       <c r="B33" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638872</v>
+        <v>638536</v>
       </c>
       <c r="R33" t="n">
-        <v>7034031</v>
+        <v>7033920</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3901,7 +3901,7 @@
         <v>133748499</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>133751033</v>
       </c>
       <c r="B35" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133750904</v>
+        <v>133754937</v>
       </c>
       <c r="B36" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638620</v>
+        <v>638759</v>
       </c>
       <c r="R36" t="n">
-        <v>7033897</v>
+        <v>7033864</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133754937</v>
+        <v>133750904</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638759</v>
+        <v>638620</v>
       </c>
       <c r="R37" t="n">
-        <v>7033864</v>
+        <v>7033897</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R38" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R39" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R40" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R41" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,10 +4674,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753992</v>
+        <v>133752438</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4685,39 +4685,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638860</v>
+        <v>638928</v>
       </c>
       <c r="R42" t="n">
-        <v>7033902</v>
+        <v>7033996</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4776,45 +4771,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133747733</v>
+        <v>133753992</v>
       </c>
       <c r="B43" t="n">
-        <v>92614</v>
+        <v>57145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>898</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638052</v>
+        <v>638860</v>
       </c>
       <c r="R43" t="n">
-        <v>7034053</v>
+        <v>7033902</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4876,7 +4876,7 @@
         <v>133753051</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4970,32 +4970,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133752438</v>
+        <v>133747733</v>
       </c>
       <c r="B45" t="n">
-        <v>80466</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638928</v>
+        <v>638052</v>
       </c>
       <c r="R45" t="n">
-        <v>7033996</v>
+        <v>7034053</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5067,32 +5067,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133752659</v>
+        <v>133754841</v>
       </c>
       <c r="B46" t="n">
-        <v>91881</v>
+        <v>92380</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639104</v>
+        <v>638763</v>
       </c>
       <c r="R46" t="n">
-        <v>7033978</v>
+        <v>7033857</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133752847</v>
+        <v>133755227</v>
       </c>
       <c r="B47" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639087</v>
+        <v>638752</v>
       </c>
       <c r="R47" t="n">
-        <v>7033883</v>
+        <v>7033861</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133754841</v>
+        <v>133752659</v>
       </c>
       <c r="B48" t="n">
-        <v>92378</v>
+        <v>91883</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638763</v>
+        <v>639104</v>
       </c>
       <c r="R48" t="n">
-        <v>7033857</v>
+        <v>7033978</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133755227</v>
+        <v>133752847</v>
       </c>
       <c r="B49" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638752</v>
+        <v>639087</v>
       </c>
       <c r="R49" t="n">
-        <v>7033861</v>
+        <v>7033883</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133747834</v>
+        <v>133748929</v>
       </c>
       <c r="B50" t="n">
-        <v>92217</v>
+        <v>89302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638050</v>
+        <v>638198</v>
       </c>
       <c r="R50" t="n">
-        <v>7034042</v>
+        <v>7034077</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133748929</v>
+        <v>133747834</v>
       </c>
       <c r="B51" t="n">
-        <v>89300</v>
+        <v>92219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638198</v>
+        <v>638050</v>
       </c>
       <c r="R51" t="n">
-        <v>7034077</v>
+        <v>7034042</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5649,10 +5649,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133748447</v>
+        <v>133752568</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638162</v>
+        <v>639034</v>
       </c>
       <c r="R52" t="n">
-        <v>7034014</v>
+        <v>7034020</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,45 +5746,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133745736</v>
+        <v>133752413</v>
       </c>
       <c r="B53" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>637993</v>
+        <v>638923</v>
       </c>
       <c r="R53" t="n">
-        <v>7034094</v>
+        <v>7034016</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,45 +5843,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133752568</v>
+        <v>133745736</v>
       </c>
       <c r="B54" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639034</v>
+        <v>637993</v>
       </c>
       <c r="R54" t="n">
-        <v>7034020</v>
+        <v>7034094</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133752413</v>
+        <v>133748447</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638923</v>
+        <v>638162</v>
       </c>
       <c r="R55" t="n">
-        <v>7034016</v>
+        <v>7034014</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133750078</v>
+        <v>133751279</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638351</v>
+        <v>638805</v>
       </c>
       <c r="R56" t="n">
-        <v>7033867</v>
+        <v>7034008</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133751279</v>
+        <v>133750078</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638805</v>
+        <v>638351</v>
       </c>
       <c r="R57" t="n">
-        <v>7034008</v>
+        <v>7033867</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6234,7 +6234,7 @@
         <v>133752304</v>
       </c>
       <c r="B58" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133749947</v>
+        <v>133752378</v>
       </c>
       <c r="B59" t="n">
-        <v>91918</v>
+        <v>89302</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638326</v>
+        <v>638902</v>
       </c>
       <c r="R59" t="n">
-        <v>7033938</v>
+        <v>7034025</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133752378</v>
+        <v>133752701</v>
       </c>
       <c r="B60" t="n">
-        <v>89300</v>
+        <v>79334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638902</v>
+        <v>639153</v>
       </c>
       <c r="R60" t="n">
-        <v>7034025</v>
+        <v>7033912</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R61" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6622,7 +6622,7 @@
         <v>133750648</v>
       </c>
       <c r="B62" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,32 +6716,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133754273</v>
+        <v>133750259</v>
       </c>
       <c r="B63" t="n">
-        <v>92378</v>
+        <v>79334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638763</v>
+        <v>638396</v>
       </c>
       <c r="R63" t="n">
-        <v>7033932</v>
+        <v>7033893</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6813,32 +6813,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133750259</v>
+        <v>133754273</v>
       </c>
       <c r="B64" t="n">
-        <v>79333</v>
+        <v>92380</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638396</v>
+        <v>638763</v>
       </c>
       <c r="R64" t="n">
-        <v>7033893</v>
+        <v>7033932</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6913,7 +6913,7 @@
         <v>133747965</v>
       </c>
       <c r="B65" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -2632,32 +2632,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133749740</v>
+        <v>133750092</v>
       </c>
       <c r="B21" t="n">
-        <v>91883</v>
+        <v>92219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638232</v>
+        <v>638348</v>
       </c>
       <c r="R21" t="n">
-        <v>7034015</v>
+        <v>7033866</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133750092</v>
+        <v>133749740</v>
       </c>
       <c r="B22" t="n">
-        <v>92219</v>
+        <v>91883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638348</v>
+        <v>638232</v>
       </c>
       <c r="R22" t="n">
-        <v>7033866</v>
+        <v>7034015</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>91883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R27" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B28" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R28" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B38" t="n">
         <v>79334</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R38" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B39" t="n">
         <v>79334</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R39" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4674,32 +4674,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133752438</v>
+        <v>133753051</v>
       </c>
       <c r="B42" t="n">
-        <v>80467</v>
+        <v>79334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638928</v>
+        <v>638997</v>
       </c>
       <c r="R42" t="n">
-        <v>7033996</v>
+        <v>7033854</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753992</v>
+        <v>133752438</v>
       </c>
       <c r="B43" t="n">
-        <v>57145</v>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4782,39 +4782,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638860</v>
+        <v>638928</v>
       </c>
       <c r="R43" t="n">
-        <v>7033902</v>
+        <v>7033996</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4873,45 +4868,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753051</v>
+        <v>133753992</v>
       </c>
       <c r="B44" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638997</v>
+        <v>638860</v>
       </c>
       <c r="R44" t="n">
-        <v>7033854</v>
+        <v>7033902</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5067,32 +5067,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133754841</v>
+        <v>133747834</v>
       </c>
       <c r="B46" t="n">
-        <v>92380</v>
+        <v>92219</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638763</v>
+        <v>638050</v>
       </c>
       <c r="R46" t="n">
-        <v>7033857</v>
+        <v>7034042</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133755227</v>
+        <v>133754841</v>
       </c>
       <c r="B47" t="n">
-        <v>91920</v>
+        <v>92380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638752</v>
+        <v>638763</v>
       </c>
       <c r="R47" t="n">
-        <v>7033861</v>
+        <v>7033857</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133752659</v>
+        <v>133755227</v>
       </c>
       <c r="B48" t="n">
-        <v>91883</v>
+        <v>91920</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639104</v>
+        <v>638752</v>
       </c>
       <c r="R48" t="n">
-        <v>7033978</v>
+        <v>7033861</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133752847</v>
+        <v>133752659</v>
       </c>
       <c r="B49" t="n">
-        <v>79334</v>
+        <v>91883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639087</v>
+        <v>639104</v>
       </c>
       <c r="R49" t="n">
-        <v>7033883</v>
+        <v>7033978</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133748929</v>
+        <v>133752847</v>
       </c>
       <c r="B50" t="n">
-        <v>89302</v>
+        <v>79334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638198</v>
+        <v>639087</v>
       </c>
       <c r="R50" t="n">
-        <v>7034077</v>
+        <v>7033883</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133747834</v>
+        <v>133748929</v>
       </c>
       <c r="B51" t="n">
-        <v>92219</v>
+        <v>89302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638050</v>
+        <v>638198</v>
       </c>
       <c r="R51" t="n">
-        <v>7034042</v>
+        <v>7034077</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2150,7 +2150,7 @@
         <v>133747890</v>
       </c>
       <c r="B16" t="n">
-        <v>92340</v>
+        <v>92346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133747219</v>
+        <v>133754875</v>
       </c>
       <c r="B17" t="n">
-        <v>80439</v>
+        <v>92346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638061</v>
+        <v>638759</v>
       </c>
       <c r="R17" t="n">
-        <v>7034028</v>
+        <v>7033860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133745580</v>
+        <v>133754154</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>92225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,34 +2352,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637989</v>
+        <v>638798</v>
       </c>
       <c r="R18" t="n">
-        <v>7034113</v>
+        <v>7033915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133754154</v>
+        <v>133747219</v>
       </c>
       <c r="B19" t="n">
-        <v>92219</v>
+        <v>80439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638798</v>
+        <v>638061</v>
       </c>
       <c r="R19" t="n">
-        <v>7033915</v>
+        <v>7034028</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133754875</v>
+        <v>133745580</v>
       </c>
       <c r="B20" t="n">
-        <v>92340</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,34 +2546,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638759</v>
+        <v>637989</v>
       </c>
       <c r="R20" t="n">
-        <v>7033860</v>
+        <v>7034113</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133750092</v>
+        <v>133749740</v>
       </c>
       <c r="B21" t="n">
-        <v>92219</v>
+        <v>91889</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638348</v>
+        <v>638232</v>
       </c>
       <c r="R21" t="n">
-        <v>7033866</v>
+        <v>7034015</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133749740</v>
+        <v>133750092</v>
       </c>
       <c r="B22" t="n">
-        <v>91883</v>
+        <v>92225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638232</v>
+        <v>638348</v>
       </c>
       <c r="R22" t="n">
-        <v>7034015</v>
+        <v>7033866</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2829,7 +2829,7 @@
         <v>133754254</v>
       </c>
       <c r="B23" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,50 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133749592</v>
+        <v>133747740</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>91926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638226</v>
+        <v>638064</v>
       </c>
       <c r="R24" t="n">
-        <v>7034023</v>
+        <v>7034062</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3025,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133747740</v>
+        <v>133745623</v>
       </c>
       <c r="B25" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,14 +3051,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638064</v>
+        <v>638018</v>
       </c>
       <c r="R25" t="n">
-        <v>7034062</v>
+        <v>7034124</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,45 +3117,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133745623</v>
+        <v>133749592</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>57145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638018</v>
+        <v>638226</v>
       </c>
       <c r="R26" t="n">
-        <v>7034124</v>
+        <v>7034023</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3222,7 +3222,7 @@
         <v>133752723</v>
       </c>
       <c r="B27" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>133755234</v>
       </c>
       <c r="B29" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>133745777</v>
       </c>
       <c r="B30" t="n">
-        <v>92219</v>
+        <v>92225</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>133748499</v>
       </c>
       <c r="B34" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>133751033</v>
       </c>
       <c r="B35" t="n">
-        <v>98003</v>
+        <v>98009</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>133754937</v>
       </c>
       <c r="B36" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>133750904</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B38" t="n">
         <v>79334</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R38" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B39" t="n">
         <v>79334</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R39" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4580,7 +4580,7 @@
         <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4674,45 +4674,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753051</v>
+        <v>133753992</v>
       </c>
       <c r="B42" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638997</v>
+        <v>638860</v>
       </c>
       <c r="R42" t="n">
-        <v>7033854</v>
+        <v>7033902</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,32 +4776,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133752438</v>
+        <v>133753051</v>
       </c>
       <c r="B43" t="n">
-        <v>80467</v>
+        <v>79334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638928</v>
+        <v>638997</v>
       </c>
       <c r="R43" t="n">
-        <v>7033996</v>
+        <v>7033854</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4873,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753992</v>
+        <v>133752438</v>
       </c>
       <c r="B44" t="n">
-        <v>57145</v>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,39 +4884,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638860</v>
+        <v>638928</v>
       </c>
       <c r="R44" t="n">
-        <v>7033902</v>
+        <v>7033996</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4973,7 +4973,7 @@
         <v>133747733</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,32 +5067,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133747834</v>
+        <v>133752659</v>
       </c>
       <c r="B46" t="n">
-        <v>92219</v>
+        <v>91889</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638050</v>
+        <v>639104</v>
       </c>
       <c r="R46" t="n">
-        <v>7034042</v>
+        <v>7033978</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133754841</v>
+        <v>133752847</v>
       </c>
       <c r="B47" t="n">
-        <v>92380</v>
+        <v>79334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638763</v>
+        <v>639087</v>
       </c>
       <c r="R47" t="n">
-        <v>7033857</v>
+        <v>7033883</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133755227</v>
+        <v>133754841</v>
       </c>
       <c r="B48" t="n">
-        <v>91920</v>
+        <v>92386</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638752</v>
+        <v>638763</v>
       </c>
       <c r="R48" t="n">
-        <v>7033861</v>
+        <v>7033857</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133752659</v>
+        <v>133755227</v>
       </c>
       <c r="B49" t="n">
-        <v>91883</v>
+        <v>91926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639104</v>
+        <v>638752</v>
       </c>
       <c r="R49" t="n">
-        <v>7033978</v>
+        <v>7033861</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133752847</v>
+        <v>133748929</v>
       </c>
       <c r="B50" t="n">
-        <v>79334</v>
+        <v>89308</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639087</v>
+        <v>638198</v>
       </c>
       <c r="R50" t="n">
-        <v>7033883</v>
+        <v>7034077</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133748929</v>
+        <v>133747834</v>
       </c>
       <c r="B51" t="n">
-        <v>89302</v>
+        <v>92225</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638198</v>
+        <v>638050</v>
       </c>
       <c r="R51" t="n">
-        <v>7034077</v>
+        <v>7034042</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133752568</v>
+        <v>133752413</v>
       </c>
       <c r="B52" t="n">
         <v>79334</v>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>639034</v>
+        <v>638923</v>
       </c>
       <c r="R52" t="n">
-        <v>7034020</v>
+        <v>7034016</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133752413</v>
+        <v>133752568</v>
       </c>
       <c r="B53" t="n">
         <v>79334</v>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638923</v>
+        <v>639034</v>
       </c>
       <c r="R53" t="n">
-        <v>7034016</v>
+        <v>7034020</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,45 +5843,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133745736</v>
+        <v>133748447</v>
       </c>
       <c r="B54" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>637993</v>
+        <v>638162</v>
       </c>
       <c r="R54" t="n">
-        <v>7034094</v>
+        <v>7034014</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133748447</v>
+        <v>133745736</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>91889</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638162</v>
+        <v>637993</v>
       </c>
       <c r="R55" t="n">
-        <v>7034014</v>
+        <v>7034094</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752378</v>
+        <v>133749947</v>
       </c>
       <c r="B59" t="n">
-        <v>89302</v>
+        <v>91926</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638902</v>
+        <v>638326</v>
       </c>
       <c r="R59" t="n">
-        <v>7034025</v>
+        <v>7033938</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133752701</v>
+        <v>133752378</v>
       </c>
       <c r="B60" t="n">
-        <v>79334</v>
+        <v>89308</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639153</v>
+        <v>638902</v>
       </c>
       <c r="R60" t="n">
-        <v>7033912</v>
+        <v>7034025</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133749947</v>
+        <v>133752701</v>
       </c>
       <c r="B61" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638326</v>
+        <v>639153</v>
       </c>
       <c r="R61" t="n">
-        <v>7033938</v>
+        <v>7033912</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6813,32 +6813,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133754273</v>
+        <v>133747965</v>
       </c>
       <c r="B64" t="n">
-        <v>92380</v>
+        <v>91889</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638763</v>
+        <v>638071</v>
       </c>
       <c r="R64" t="n">
-        <v>7033932</v>
+        <v>7034053</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133747965</v>
+        <v>133754273</v>
       </c>
       <c r="B65" t="n">
-        <v>91883</v>
+        <v>92386</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638071</v>
+        <v>638763</v>
       </c>
       <c r="R65" t="n">
-        <v>7034053</v>
+        <v>7033932</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7004,6 +7004,107 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133755120</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92298</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>638785</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7033861</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>92348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R14" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133747890</v>
+        <v>133751145</v>
       </c>
       <c r="B16" t="n">
-        <v>92346</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638059</v>
+        <v>638754</v>
       </c>
       <c r="R16" t="n">
-        <v>7034046</v>
+        <v>7033961</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133754875</v>
+        <v>133754154</v>
       </c>
       <c r="B17" t="n">
-        <v>92346</v>
+        <v>92227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638759</v>
+        <v>638798</v>
       </c>
       <c r="R17" t="n">
-        <v>7033860</v>
+        <v>7033915</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133754154</v>
+        <v>133754875</v>
       </c>
       <c r="B18" t="n">
-        <v>92225</v>
+        <v>92348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6040186</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638798</v>
+        <v>638759</v>
       </c>
       <c r="R18" t="n">
-        <v>7033915</v>
+        <v>7033860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133749740</v>
+        <v>133750092</v>
       </c>
       <c r="B21" t="n">
-        <v>91889</v>
+        <v>92227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638232</v>
+        <v>638348</v>
       </c>
       <c r="R21" t="n">
-        <v>7034015</v>
+        <v>7033866</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133750092</v>
+        <v>133749740</v>
       </c>
       <c r="B22" t="n">
-        <v>92225</v>
+        <v>91891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638348</v>
+        <v>638232</v>
       </c>
       <c r="R22" t="n">
-        <v>7033866</v>
+        <v>7034015</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2829,7 +2829,7 @@
         <v>133754254</v>
       </c>
       <c r="B23" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>133747740</v>
       </c>
       <c r="B24" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>133745623</v>
       </c>
       <c r="B25" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>91889</v>
+        <v>79334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R28" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3413,45 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133755234</v>
+        <v>133745777</v>
       </c>
       <c r="B29" t="n">
-        <v>91889</v>
+        <v>92227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638761</v>
+        <v>638007</v>
       </c>
       <c r="R29" t="n">
-        <v>7033856</v>
+        <v>7034104</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,45 +3510,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133745777</v>
+        <v>133747269</v>
       </c>
       <c r="B30" t="n">
-        <v>92225</v>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638007</v>
+        <v>638060</v>
       </c>
       <c r="R30" t="n">
-        <v>7034104</v>
+        <v>7034027</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133747269</v>
+        <v>133755234</v>
       </c>
       <c r="B31" t="n">
-        <v>80468</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638060</v>
+        <v>638761</v>
       </c>
       <c r="R31" t="n">
-        <v>7034027</v>
+        <v>7033856</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3707,7 +3707,7 @@
         <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>133748499</v>
       </c>
       <c r="B34" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>133751033</v>
       </c>
       <c r="B35" t="n">
-        <v>98009</v>
+        <v>98011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133754937</v>
+        <v>133750904</v>
       </c>
       <c r="B36" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638759</v>
+        <v>638620</v>
       </c>
       <c r="R36" t="n">
-        <v>7033864</v>
+        <v>7033897</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133750904</v>
+        <v>133754937</v>
       </c>
       <c r="B37" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638620</v>
+        <v>638759</v>
       </c>
       <c r="R37" t="n">
-        <v>7033897</v>
+        <v>7033864</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R40" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B41" t="n">
-        <v>91926</v>
+        <v>79334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R41" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4973,7 +4973,7 @@
         <v>133747733</v>
       </c>
       <c r="B45" t="n">
-        <v>92622</v>
+        <v>92624</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,32 +5067,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133752659</v>
+        <v>133752847</v>
       </c>
       <c r="B46" t="n">
-        <v>91889</v>
+        <v>79334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639104</v>
+        <v>639087</v>
       </c>
       <c r="R46" t="n">
-        <v>7033978</v>
+        <v>7033883</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133752847</v>
+        <v>133755227</v>
       </c>
       <c r="B47" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639087</v>
+        <v>638752</v>
       </c>
       <c r="R47" t="n">
-        <v>7033883</v>
+        <v>7033861</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5264,7 +5264,7 @@
         <v>133754841</v>
       </c>
       <c r="B48" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133755227</v>
+        <v>133752659</v>
       </c>
       <c r="B49" t="n">
-        <v>91926</v>
+        <v>91891</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638752</v>
+        <v>639104</v>
       </c>
       <c r="R49" t="n">
-        <v>7033861</v>
+        <v>7033978</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5458,7 +5458,7 @@
         <v>133748929</v>
       </c>
       <c r="B50" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>133747834</v>
       </c>
       <c r="B51" t="n">
-        <v>92225</v>
+        <v>92227</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5649,45 +5649,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133752413</v>
+        <v>133745736</v>
       </c>
       <c r="B52" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638923</v>
+        <v>637993</v>
       </c>
       <c r="R52" t="n">
-        <v>7034016</v>
+        <v>7034094</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133752568</v>
+        <v>133748447</v>
       </c>
       <c r="B53" t="n">
         <v>79334</v>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639034</v>
+        <v>638162</v>
       </c>
       <c r="R53" t="n">
-        <v>7034020</v>
+        <v>7034014</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133748447</v>
+        <v>133752568</v>
       </c>
       <c r="B54" t="n">
         <v>79334</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638162</v>
+        <v>639034</v>
       </c>
       <c r="R54" t="n">
-        <v>7034014</v>
+        <v>7034020</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133745736</v>
+        <v>133752413</v>
       </c>
       <c r="B55" t="n">
-        <v>91889</v>
+        <v>79334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>637993</v>
+        <v>638923</v>
       </c>
       <c r="R55" t="n">
-        <v>7034094</v>
+        <v>7034016</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133749947</v>
+        <v>133752701</v>
       </c>
       <c r="B59" t="n">
-        <v>91926</v>
+        <v>79334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638326</v>
+        <v>639153</v>
       </c>
       <c r="R59" t="n">
-        <v>7033938</v>
+        <v>7033912</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133752378</v>
+        <v>133749947</v>
       </c>
       <c r="B60" t="n">
-        <v>89308</v>
+        <v>91928</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638902</v>
+        <v>638326</v>
       </c>
       <c r="R60" t="n">
-        <v>7034025</v>
+        <v>7033938</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133752701</v>
+        <v>133752378</v>
       </c>
       <c r="B61" t="n">
-        <v>79334</v>
+        <v>89310</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639153</v>
+        <v>638902</v>
       </c>
       <c r="R61" t="n">
-        <v>7033912</v>
+        <v>7034025</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6619,32 +6619,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133750648</v>
+        <v>133747965</v>
       </c>
       <c r="B62" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638588</v>
+        <v>638071</v>
       </c>
       <c r="R62" t="n">
-        <v>7033862</v>
+        <v>7034053</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6716,32 +6716,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133750259</v>
+        <v>133754273</v>
       </c>
       <c r="B63" t="n">
-        <v>79334</v>
+        <v>92388</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638396</v>
+        <v>638763</v>
       </c>
       <c r="R63" t="n">
-        <v>7033893</v>
+        <v>7033932</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6813,32 +6813,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133747965</v>
+        <v>133750648</v>
       </c>
       <c r="B64" t="n">
-        <v>91889</v>
+        <v>79334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638071</v>
+        <v>638588</v>
       </c>
       <c r="R64" t="n">
-        <v>7034053</v>
+        <v>7033862</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133754273</v>
+        <v>133750259</v>
       </c>
       <c r="B65" t="n">
-        <v>92386</v>
+        <v>79334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638763</v>
+        <v>638396</v>
       </c>
       <c r="R65" t="n">
-        <v>7033932</v>
+        <v>7033893</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7010,7 +7010,7 @@
         <v>133755120</v>
       </c>
       <c r="B66" t="n">
-        <v>92298</v>
+        <v>92300</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -2050,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B15" t="n">
         <v>79334</v>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R15" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133751145</v>
+        <v>133748002</v>
       </c>
       <c r="B16" t="n">
         <v>79334</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638754</v>
+        <v>638084</v>
       </c>
       <c r="R16" t="n">
-        <v>7033961</v>
+        <v>7034064</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133754875</v>
+        <v>133747219</v>
       </c>
       <c r="B18" t="n">
-        <v>92348</v>
+        <v>80439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638759</v>
+        <v>638061</v>
       </c>
       <c r="R18" t="n">
-        <v>7033860</v>
+        <v>7034028</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133747219</v>
+        <v>133745580</v>
       </c>
       <c r="B19" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,34 +2449,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638061</v>
+        <v>637989</v>
       </c>
       <c r="R19" t="n">
-        <v>7034028</v>
+        <v>7034113</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133745580</v>
+        <v>133754875</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>92348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,34 +2546,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637989</v>
+        <v>638759</v>
       </c>
       <c r="R20" t="n">
-        <v>7034113</v>
+        <v>7033860</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R27" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B28" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R28" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B40" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R40" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R41" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,50 +4674,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753992</v>
+        <v>133753051</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638860</v>
+        <v>638997</v>
       </c>
       <c r="R42" t="n">
-        <v>7033902</v>
+        <v>7033854</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4776,32 +4771,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753051</v>
+        <v>133752438</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638997</v>
+        <v>638928</v>
       </c>
       <c r="R43" t="n">
-        <v>7033854</v>
+        <v>7033996</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4873,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133752438</v>
+        <v>133753992</v>
       </c>
       <c r="B44" t="n">
-        <v>80467</v>
+        <v>57145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4884,34 +4879,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638928</v>
+        <v>638860</v>
       </c>
       <c r="R44" t="n">
-        <v>7033996</v>
+        <v>7033902</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5649,45 +5649,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133745736</v>
+        <v>133752568</v>
       </c>
       <c r="B52" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>637993</v>
+        <v>639034</v>
       </c>
       <c r="R52" t="n">
-        <v>7034094</v>
+        <v>7034020</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133748447</v>
+        <v>133752413</v>
       </c>
       <c r="B53" t="n">
         <v>79334</v>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638162</v>
+        <v>638923</v>
       </c>
       <c r="R53" t="n">
-        <v>7034014</v>
+        <v>7034016</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,45 +5843,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133752568</v>
+        <v>133745736</v>
       </c>
       <c r="B54" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639034</v>
+        <v>637993</v>
       </c>
       <c r="R54" t="n">
-        <v>7034020</v>
+        <v>7034094</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133752413</v>
+        <v>133748447</v>
       </c>
       <c r="B55" t="n">
         <v>79334</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638923</v>
+        <v>638162</v>
       </c>
       <c r="R55" t="n">
-        <v>7034016</v>
+        <v>7034014</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133749947</v>
+        <v>133752378</v>
       </c>
       <c r="B60" t="n">
-        <v>91928</v>
+        <v>89310</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638326</v>
+        <v>638902</v>
       </c>
       <c r="R60" t="n">
-        <v>7033938</v>
+        <v>7034025</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133752378</v>
+        <v>133749947</v>
       </c>
       <c r="B61" t="n">
-        <v>89310</v>
+        <v>91928</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638902</v>
+        <v>638326</v>
       </c>
       <c r="R61" t="n">
-        <v>7034025</v>
+        <v>7033938</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R28" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R40" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B41" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R41" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,45 +4674,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753051</v>
+        <v>133753992</v>
       </c>
       <c r="B42" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638997</v>
+        <v>638860</v>
       </c>
       <c r="R42" t="n">
-        <v>7033854</v>
+        <v>7033902</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,32 +4776,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133752438</v>
+        <v>133753051</v>
       </c>
       <c r="B43" t="n">
-        <v>80467</v>
+        <v>79334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638928</v>
+        <v>638997</v>
       </c>
       <c r="R43" t="n">
-        <v>7033996</v>
+        <v>7033854</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4873,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753992</v>
+        <v>133752438</v>
       </c>
       <c r="B44" t="n">
-        <v>57145</v>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,39 +4884,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638860</v>
+        <v>638928</v>
       </c>
       <c r="R44" t="n">
-        <v>7033902</v>
+        <v>7033996</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -4674,50 +4674,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753992</v>
+        <v>133753051</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>79334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638860</v>
+        <v>638997</v>
       </c>
       <c r="R42" t="n">
-        <v>7033902</v>
+        <v>7033854</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4776,32 +4771,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753051</v>
+        <v>133752438</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638997</v>
+        <v>638928</v>
       </c>
       <c r="R43" t="n">
-        <v>7033854</v>
+        <v>7033996</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4873,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133752438</v>
+        <v>133753992</v>
       </c>
       <c r="B44" t="n">
-        <v>80467</v>
+        <v>57145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4884,34 +4879,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638928</v>
+        <v>638860</v>
       </c>
       <c r="R44" t="n">
-        <v>7033996</v>
+        <v>7033902</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R27" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B28" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R28" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B40" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R40" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R41" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,45 +4674,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753051</v>
+        <v>133753992</v>
       </c>
       <c r="B42" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638997</v>
+        <v>638860</v>
       </c>
       <c r="R42" t="n">
-        <v>7033854</v>
+        <v>7033902</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,32 +4776,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133752438</v>
+        <v>133753051</v>
       </c>
       <c r="B43" t="n">
-        <v>80467</v>
+        <v>79334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4806,10 +4811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638928</v>
+        <v>638997</v>
       </c>
       <c r="R43" t="n">
-        <v>7033996</v>
+        <v>7033854</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,10 +4873,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753992</v>
+        <v>133752438</v>
       </c>
       <c r="B44" t="n">
-        <v>57145</v>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,39 +4884,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638860</v>
+        <v>638928</v>
       </c>
       <c r="R44" t="n">
-        <v>7033902</v>
+        <v>7033996</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752701</v>
+        <v>133752378</v>
       </c>
       <c r="B59" t="n">
-        <v>79334</v>
+        <v>89310</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>639153</v>
+        <v>638902</v>
       </c>
       <c r="R59" t="n">
-        <v>7033912</v>
+        <v>7034025</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133752378</v>
+        <v>133752701</v>
       </c>
       <c r="B60" t="n">
-        <v>89310</v>
+        <v>79334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638902</v>
+        <v>639153</v>
       </c>
       <c r="R60" t="n">
-        <v>7034025</v>
+        <v>7033912</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1859,7 +1859,7 @@
         <v>133748644</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133747890</v>
+        <v>133748002</v>
       </c>
       <c r="B14" t="n">
-        <v>92348</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638059</v>
+        <v>638084</v>
       </c>
       <c r="R14" t="n">
-        <v>7034046</v>
+        <v>7034064</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>92339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R15" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R16" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133754154</v>
+        <v>133745580</v>
       </c>
       <c r="B17" t="n">
-        <v>92227</v>
+        <v>79348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,34 +2255,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638798</v>
+        <v>637989</v>
       </c>
       <c r="R17" t="n">
-        <v>7033915</v>
+        <v>7034113</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2344,7 +2344,7 @@
         <v>133747219</v>
       </c>
       <c r="B18" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133745580</v>
+        <v>133754875</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>92339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,34 +2449,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637989</v>
+        <v>638759</v>
       </c>
       <c r="R19" t="n">
-        <v>7034113</v>
+        <v>7033860</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133754875</v>
+        <v>133754154</v>
       </c>
       <c r="B20" t="n">
-        <v>92348</v>
+        <v>92218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638759</v>
+        <v>638798</v>
       </c>
       <c r="R20" t="n">
-        <v>7033860</v>
+        <v>7033915</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2635,7 +2635,7 @@
         <v>133750092</v>
       </c>
       <c r="B21" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>133749740</v>
       </c>
       <c r="B22" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>133754254</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>133747740</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>133745623</v>
       </c>
       <c r="B25" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>133749592</v>
       </c>
       <c r="B26" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>91891</v>
+        <v>79348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R28" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3413,45 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133745777</v>
+        <v>133755234</v>
       </c>
       <c r="B29" t="n">
-        <v>92227</v>
+        <v>91910</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638007</v>
+        <v>638761</v>
       </c>
       <c r="R29" t="n">
-        <v>7034104</v>
+        <v>7033856</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,45 +3510,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133747269</v>
+        <v>133745777</v>
       </c>
       <c r="B30" t="n">
-        <v>80468</v>
+        <v>92218</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638060</v>
+        <v>638007</v>
       </c>
       <c r="R30" t="n">
-        <v>7034027</v>
+        <v>7034104</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133755234</v>
+        <v>133747269</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>80482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638761</v>
+        <v>638060</v>
       </c>
       <c r="R31" t="n">
-        <v>7033856</v>
+        <v>7034027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3707,7 +3707,7 @@
         <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>133750539</v>
       </c>
       <c r="B33" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133748499</v>
+        <v>133751033</v>
       </c>
       <c r="B34" t="n">
-        <v>91891</v>
+        <v>98039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638163</v>
+        <v>638655</v>
       </c>
       <c r="R34" t="n">
-        <v>7034015</v>
+        <v>7033936</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133751033</v>
+        <v>133748499</v>
       </c>
       <c r="B35" t="n">
-        <v>98011</v>
+        <v>91910</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638655</v>
+        <v>638163</v>
       </c>
       <c r="R35" t="n">
-        <v>7033936</v>
+        <v>7034015</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133750904</v>
+        <v>133754937</v>
       </c>
       <c r="B36" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638620</v>
+        <v>638759</v>
       </c>
       <c r="R36" t="n">
-        <v>7033897</v>
+        <v>7033864</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133754937</v>
+        <v>133750904</v>
       </c>
       <c r="B37" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638759</v>
+        <v>638620</v>
       </c>
       <c r="R37" t="n">
-        <v>7033864</v>
+        <v>7033897</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4289,7 +4289,7 @@
         <v>133752639</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>133748793</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>133754117</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4674,50 +4674,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753992</v>
+        <v>133753051</v>
       </c>
       <c r="B42" t="n">
-        <v>57145</v>
+        <v>79348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638860</v>
+        <v>638997</v>
       </c>
       <c r="R42" t="n">
-        <v>7033902</v>
+        <v>7033854</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4776,32 +4771,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753051</v>
+        <v>133752438</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>80481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638997</v>
+        <v>638928</v>
       </c>
       <c r="R43" t="n">
-        <v>7033854</v>
+        <v>7033996</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4873,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133752438</v>
+        <v>133753992</v>
       </c>
       <c r="B44" t="n">
-        <v>80467</v>
+        <v>57152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4884,34 +4879,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638928</v>
+        <v>638860</v>
       </c>
       <c r="R44" t="n">
-        <v>7033996</v>
+        <v>7033902</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4973,7 +4973,7 @@
         <v>133747733</v>
       </c>
       <c r="B45" t="n">
-        <v>92624</v>
+        <v>92662</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,10 +5067,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133752847</v>
+        <v>133748929</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>89328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>639087</v>
+        <v>638198</v>
       </c>
       <c r="R46" t="n">
-        <v>7033883</v>
+        <v>7034077</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133755227</v>
+        <v>133752659</v>
       </c>
       <c r="B47" t="n">
-        <v>91928</v>
+        <v>91910</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638752</v>
+        <v>639104</v>
       </c>
       <c r="R47" t="n">
-        <v>7033861</v>
+        <v>7033978</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5264,7 +5264,7 @@
         <v>133754841</v>
       </c>
       <c r="B48" t="n">
-        <v>92388</v>
+        <v>92379</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133752659</v>
+        <v>133752847</v>
       </c>
       <c r="B49" t="n">
-        <v>91891</v>
+        <v>79348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639104</v>
+        <v>639087</v>
       </c>
       <c r="R49" t="n">
-        <v>7033978</v>
+        <v>7033883</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133748929</v>
+        <v>133755227</v>
       </c>
       <c r="B50" t="n">
-        <v>89310</v>
+        <v>91947</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638198</v>
+        <v>638752</v>
       </c>
       <c r="R50" t="n">
-        <v>7034077</v>
+        <v>7033861</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5555,7 +5555,7 @@
         <v>133747834</v>
       </c>
       <c r="B51" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5649,10 +5649,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133752568</v>
+        <v>133748447</v>
       </c>
       <c r="B52" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>639034</v>
+        <v>638162</v>
       </c>
       <c r="R52" t="n">
-        <v>7034020</v>
+        <v>7034014</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,10 +5746,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133752413</v>
+        <v>133752568</v>
       </c>
       <c r="B53" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638923</v>
+        <v>639034</v>
       </c>
       <c r="R53" t="n">
-        <v>7034016</v>
+        <v>7034020</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,45 +5843,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133745736</v>
+        <v>133752413</v>
       </c>
       <c r="B54" t="n">
-        <v>91891</v>
+        <v>79348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>637993</v>
+        <v>638923</v>
       </c>
       <c r="R54" t="n">
-        <v>7034094</v>
+        <v>7034016</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133748447</v>
+        <v>133745736</v>
       </c>
       <c r="B55" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638162</v>
+        <v>637993</v>
       </c>
       <c r="R55" t="n">
-        <v>7034014</v>
+        <v>7034094</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6040,7 +6040,7 @@
         <v>133751279</v>
       </c>
       <c r="B56" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>133750078</v>
       </c>
       <c r="B57" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>133752304</v>
       </c>
       <c r="B58" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752378</v>
+        <v>133752701</v>
       </c>
       <c r="B59" t="n">
-        <v>89310</v>
+        <v>79348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638902</v>
+        <v>639153</v>
       </c>
       <c r="R59" t="n">
-        <v>7034025</v>
+        <v>7033912</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133752701</v>
+        <v>133752378</v>
       </c>
       <c r="B60" t="n">
-        <v>79334</v>
+        <v>89328</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>639153</v>
+        <v>638902</v>
       </c>
       <c r="R60" t="n">
-        <v>7033912</v>
+        <v>7034025</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6525,7 +6525,7 @@
         <v>133749947</v>
       </c>
       <c r="B61" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>133747965</v>
       </c>
       <c r="B62" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>133754273</v>
       </c>
       <c r="B63" t="n">
-        <v>92388</v>
+        <v>92379</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>133750648</v>
       </c>
       <c r="B64" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>133750259</v>
       </c>
       <c r="B65" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>133755120</v>
       </c>
       <c r="B66" t="n">
-        <v>92300</v>
+        <v>92291</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133745580</v>
+        <v>133747219</v>
       </c>
       <c r="B17" t="n">
-        <v>79348</v>
+        <v>80453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,34 +2255,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637989</v>
+        <v>638061</v>
       </c>
       <c r="R17" t="n">
-        <v>7034113</v>
+        <v>7034028</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133747219</v>
+        <v>133745580</v>
       </c>
       <c r="B18" t="n">
-        <v>80453</v>
+        <v>79348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,34 +2352,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638061</v>
+        <v>637989</v>
       </c>
       <c r="R18" t="n">
-        <v>7034028</v>
+        <v>7034113</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133750092</v>
+        <v>133749740</v>
       </c>
       <c r="B21" t="n">
-        <v>92218</v>
+        <v>91910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638348</v>
+        <v>638232</v>
       </c>
       <c r="R21" t="n">
-        <v>7033866</v>
+        <v>7034015</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133749740</v>
+        <v>133750092</v>
       </c>
       <c r="B22" t="n">
-        <v>91910</v>
+        <v>92218</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638232</v>
+        <v>638348</v>
       </c>
       <c r="R22" t="n">
-        <v>7034015</v>
+        <v>7033866</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3020,45 +3020,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133745623</v>
+        <v>133749592</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>57152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638018</v>
+        <v>638226</v>
       </c>
       <c r="R25" t="n">
-        <v>7034124</v>
+        <v>7034023</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,50 +3122,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133749592</v>
+        <v>133745623</v>
       </c>
       <c r="B26" t="n">
-        <v>57152</v>
+        <v>91947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638226</v>
+        <v>638018</v>
       </c>
       <c r="R26" t="n">
-        <v>7034023</v>
+        <v>7034124</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3413,45 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133755234</v>
+        <v>133745777</v>
       </c>
       <c r="B29" t="n">
-        <v>91910</v>
+        <v>92218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638761</v>
+        <v>638007</v>
       </c>
       <c r="R29" t="n">
-        <v>7033856</v>
+        <v>7034104</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,45 +3510,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133745777</v>
+        <v>133747269</v>
       </c>
       <c r="B30" t="n">
-        <v>92218</v>
+        <v>80482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638007</v>
+        <v>638060</v>
       </c>
       <c r="R30" t="n">
-        <v>7034104</v>
+        <v>7034027</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133747269</v>
+        <v>133755234</v>
       </c>
       <c r="B31" t="n">
-        <v>80482</v>
+        <v>91910</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638060</v>
+        <v>638761</v>
       </c>
       <c r="R31" t="n">
-        <v>7034027</v>
+        <v>7033856</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B38" t="n">
         <v>79348</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R38" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B39" t="n">
         <v>79348</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R39" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B40" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R40" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B41" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R41" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4674,32 +4674,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133753051</v>
+        <v>133747733</v>
       </c>
       <c r="B42" t="n">
-        <v>79348</v>
+        <v>92662</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638997</v>
+        <v>638052</v>
       </c>
       <c r="R42" t="n">
-        <v>7033854</v>
+        <v>7034053</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133752438</v>
+        <v>133753992</v>
       </c>
       <c r="B43" t="n">
-        <v>80481</v>
+        <v>57152</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4782,34 +4782,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638928</v>
+        <v>638860</v>
       </c>
       <c r="R43" t="n">
-        <v>7033996</v>
+        <v>7033902</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,50 +4873,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753992</v>
+        <v>133753051</v>
       </c>
       <c r="B44" t="n">
-        <v>57152</v>
+        <v>79348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638860</v>
+        <v>638997</v>
       </c>
       <c r="R44" t="n">
-        <v>7033902</v>
+        <v>7033854</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4970,32 +4970,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133747733</v>
+        <v>133752438</v>
       </c>
       <c r="B45" t="n">
-        <v>92662</v>
+        <v>80481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>898</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638052</v>
+        <v>638928</v>
       </c>
       <c r="R45" t="n">
-        <v>7034053</v>
+        <v>7033996</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5067,32 +5067,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133748929</v>
+        <v>133754841</v>
       </c>
       <c r="B46" t="n">
-        <v>89328</v>
+        <v>92379</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638198</v>
+        <v>638763</v>
       </c>
       <c r="R46" t="n">
-        <v>7034077</v>
+        <v>7033857</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133752659</v>
+        <v>133752847</v>
       </c>
       <c r="B47" t="n">
-        <v>91910</v>
+        <v>79348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639104</v>
+        <v>639087</v>
       </c>
       <c r="R47" t="n">
-        <v>7033978</v>
+        <v>7033883</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,32 +5261,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133754841</v>
+        <v>133755227</v>
       </c>
       <c r="B48" t="n">
-        <v>92379</v>
+        <v>91947</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638763</v>
+        <v>638752</v>
       </c>
       <c r="R48" t="n">
-        <v>7033857</v>
+        <v>7033861</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133752847</v>
+        <v>133747834</v>
       </c>
       <c r="B49" t="n">
-        <v>79348</v>
+        <v>92218</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>639087</v>
+        <v>638050</v>
       </c>
       <c r="R49" t="n">
-        <v>7033883</v>
+        <v>7034042</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133755227</v>
+        <v>133752659</v>
       </c>
       <c r="B50" t="n">
-        <v>91947</v>
+        <v>91910</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638752</v>
+        <v>639104</v>
       </c>
       <c r="R50" t="n">
-        <v>7033861</v>
+        <v>7033978</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133747834</v>
+        <v>133748929</v>
       </c>
       <c r="B51" t="n">
-        <v>92218</v>
+        <v>89328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638050</v>
+        <v>638198</v>
       </c>
       <c r="R51" t="n">
-        <v>7034042</v>
+        <v>7034077</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133748447</v>
+        <v>133752568</v>
       </c>
       <c r="B52" t="n">
         <v>79348</v>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638162</v>
+        <v>639034</v>
       </c>
       <c r="R52" t="n">
-        <v>7034014</v>
+        <v>7034020</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133752568</v>
+        <v>133752413</v>
       </c>
       <c r="B53" t="n">
         <v>79348</v>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>639034</v>
+        <v>638923</v>
       </c>
       <c r="R53" t="n">
-        <v>7034020</v>
+        <v>7034016</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133752413</v>
+        <v>133748447</v>
       </c>
       <c r="B54" t="n">
         <v>79348</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638923</v>
+        <v>638162</v>
       </c>
       <c r="R54" t="n">
-        <v>7034016</v>
+        <v>7034014</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133751279</v>
+        <v>133750078</v>
       </c>
       <c r="B56" t="n">
         <v>79348</v>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638805</v>
+        <v>638351</v>
       </c>
       <c r="R56" t="n">
-        <v>7034008</v>
+        <v>7033867</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133750078</v>
+        <v>133751279</v>
       </c>
       <c r="B57" t="n">
         <v>79348</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638351</v>
+        <v>638805</v>
       </c>
       <c r="R57" t="n">
-        <v>7033867</v>
+        <v>7034008</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B59" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R59" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133749947</v>
+        <v>133752701</v>
       </c>
       <c r="B61" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638326</v>
+        <v>639153</v>
       </c>
       <c r="R61" t="n">
-        <v>7033938</v>
+        <v>7033912</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6716,32 +6716,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133754273</v>
+        <v>133750648</v>
       </c>
       <c r="B63" t="n">
-        <v>92379</v>
+        <v>79348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638763</v>
+        <v>638588</v>
       </c>
       <c r="R63" t="n">
-        <v>7033932</v>
+        <v>7033862</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133750648</v>
+        <v>133750259</v>
       </c>
       <c r="B64" t="n">
         <v>79348</v>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638588</v>
+        <v>638396</v>
       </c>
       <c r="R64" t="n">
-        <v>7033862</v>
+        <v>7033893</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133750259</v>
+        <v>133754273</v>
       </c>
       <c r="B65" t="n">
-        <v>79348</v>
+        <v>92379</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638396</v>
+        <v>638763</v>
       </c>
       <c r="R65" t="n">
-        <v>7033893</v>
+        <v>7033932</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1859,7 +1859,7 @@
         <v>133748644</v>
       </c>
       <c r="B13" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R14" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133747890</v>
+        <v>133748002</v>
       </c>
       <c r="B15" t="n">
-        <v>92339</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638059</v>
+        <v>638084</v>
       </c>
       <c r="R15" t="n">
-        <v>7034046</v>
+        <v>7034064</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B16" t="n">
-        <v>79348</v>
+        <v>92349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R16" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133747219</v>
+        <v>133754875</v>
       </c>
       <c r="B17" t="n">
-        <v>80453</v>
+        <v>92349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638061</v>
+        <v>638759</v>
       </c>
       <c r="R17" t="n">
-        <v>7034028</v>
+        <v>7033860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133745580</v>
+        <v>133754154</v>
       </c>
       <c r="B18" t="n">
-        <v>79348</v>
+        <v>92228</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,34 +2352,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637989</v>
+        <v>638798</v>
       </c>
       <c r="R18" t="n">
-        <v>7034113</v>
+        <v>7033915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133754875</v>
+        <v>133747219</v>
       </c>
       <c r="B19" t="n">
-        <v>92339</v>
+        <v>80473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638759</v>
+        <v>638061</v>
       </c>
       <c r="R19" t="n">
-        <v>7033860</v>
+        <v>7034028</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133754154</v>
+        <v>133745580</v>
       </c>
       <c r="B20" t="n">
-        <v>92218</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,34 +2546,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638798</v>
+        <v>637989</v>
       </c>
       <c r="R20" t="n">
-        <v>7033915</v>
+        <v>7034113</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2635,7 +2635,7 @@
         <v>133749740</v>
       </c>
       <c r="B21" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>133750092</v>
       </c>
       <c r="B22" t="n">
-        <v>92218</v>
+        <v>92228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>133754254</v>
       </c>
       <c r="B23" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133747740</v>
+        <v>133745623</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,14 +2954,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638064</v>
+        <v>638018</v>
       </c>
       <c r="R24" t="n">
-        <v>7034062</v>
+        <v>7034124</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3020,50 +3020,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133749592</v>
+        <v>133747740</v>
       </c>
       <c r="B25" t="n">
-        <v>57152</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638226</v>
+        <v>638064</v>
       </c>
       <c r="R25" t="n">
-        <v>7034023</v>
+        <v>7034062</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,45 +3117,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133745623</v>
+        <v>133749592</v>
       </c>
       <c r="B26" t="n">
-        <v>91947</v>
+        <v>57162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638018</v>
+        <v>638226</v>
       </c>
       <c r="R26" t="n">
-        <v>7034124</v>
+        <v>7034023</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B27" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R27" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B28" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R28" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3413,45 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133745777</v>
+        <v>133747269</v>
       </c>
       <c r="B29" t="n">
-        <v>92218</v>
+        <v>80478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638007</v>
+        <v>638060</v>
       </c>
       <c r="R29" t="n">
-        <v>7034104</v>
+        <v>7034027</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,45 +3510,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133747269</v>
+        <v>133745777</v>
       </c>
       <c r="B30" t="n">
-        <v>80482</v>
+        <v>92228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638060</v>
+        <v>638007</v>
       </c>
       <c r="R30" t="n">
-        <v>7034027</v>
+        <v>7034104</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3610,7 +3610,7 @@
         <v>133755234</v>
       </c>
       <c r="B31" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>133750539</v>
       </c>
       <c r="B33" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133751033</v>
+        <v>133748499</v>
       </c>
       <c r="B34" t="n">
-        <v>98039</v>
+        <v>91920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638655</v>
+        <v>638163</v>
       </c>
       <c r="R34" t="n">
-        <v>7033936</v>
+        <v>7034015</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133748499</v>
+        <v>133751033</v>
       </c>
       <c r="B35" t="n">
-        <v>91910</v>
+        <v>98049</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638163</v>
+        <v>638655</v>
       </c>
       <c r="R35" t="n">
-        <v>7034015</v>
+        <v>7033936</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4095,7 +4095,7 @@
         <v>133754937</v>
       </c>
       <c r="B36" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>133750904</v>
       </c>
       <c r="B37" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>133748793</v>
       </c>
       <c r="B38" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>133752639</v>
       </c>
       <c r="B39" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B40" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R40" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R41" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4677,7 +4677,7 @@
         <v>133747733</v>
       </c>
       <c r="B42" t="n">
-        <v>92662</v>
+        <v>92672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>133753992</v>
       </c>
       <c r="B43" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>133753051</v>
       </c>
       <c r="B44" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>133752438</v>
       </c>
       <c r="B45" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5067,32 +5067,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133754841</v>
+        <v>133752659</v>
       </c>
       <c r="B46" t="n">
-        <v>92379</v>
+        <v>91920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638763</v>
+        <v>639104</v>
       </c>
       <c r="R46" t="n">
-        <v>7033857</v>
+        <v>7033978</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133752847</v>
+        <v>133754841</v>
       </c>
       <c r="B47" t="n">
-        <v>79348</v>
+        <v>92389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639087</v>
+        <v>638763</v>
       </c>
       <c r="R47" t="n">
-        <v>7033883</v>
+        <v>7033857</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133755227</v>
+        <v>133752847</v>
       </c>
       <c r="B48" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638752</v>
+        <v>639087</v>
       </c>
       <c r="R48" t="n">
-        <v>7033861</v>
+        <v>7033883</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133747834</v>
+        <v>133755227</v>
       </c>
       <c r="B49" t="n">
-        <v>92218</v>
+        <v>91957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638050</v>
+        <v>638752</v>
       </c>
       <c r="R49" t="n">
-        <v>7034042</v>
+        <v>7033861</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133752659</v>
+        <v>133748929</v>
       </c>
       <c r="B50" t="n">
-        <v>91910</v>
+        <v>89338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>639104</v>
+        <v>638198</v>
       </c>
       <c r="R50" t="n">
-        <v>7033978</v>
+        <v>7034077</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133748929</v>
+        <v>133747834</v>
       </c>
       <c r="B51" t="n">
-        <v>89328</v>
+        <v>92228</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638198</v>
+        <v>638050</v>
       </c>
       <c r="R51" t="n">
-        <v>7034077</v>
+        <v>7034042</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5649,45 +5649,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133752568</v>
+        <v>133745736</v>
       </c>
       <c r="B52" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>639034</v>
+        <v>637993</v>
       </c>
       <c r="R52" t="n">
-        <v>7034020</v>
+        <v>7034094</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,10 +5746,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133752413</v>
+        <v>133748447</v>
       </c>
       <c r="B53" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638923</v>
+        <v>638162</v>
       </c>
       <c r="R53" t="n">
-        <v>7034016</v>
+        <v>7034014</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133748447</v>
+        <v>133752568</v>
       </c>
       <c r="B54" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638162</v>
+        <v>639034</v>
       </c>
       <c r="R54" t="n">
-        <v>7034014</v>
+        <v>7034020</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133745736</v>
+        <v>133752413</v>
       </c>
       <c r="B55" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>637993</v>
+        <v>638923</v>
       </c>
       <c r="R55" t="n">
-        <v>7034094</v>
+        <v>7034016</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133750078</v>
+        <v>133751279</v>
       </c>
       <c r="B56" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638351</v>
+        <v>638805</v>
       </c>
       <c r="R56" t="n">
-        <v>7033867</v>
+        <v>7034008</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133751279</v>
+        <v>133750078</v>
       </c>
       <c r="B57" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638805</v>
+        <v>638351</v>
       </c>
       <c r="R57" t="n">
-        <v>7034008</v>
+        <v>7033867</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6234,7 +6234,7 @@
         <v>133752304</v>
       </c>
       <c r="B58" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133749947</v>
+        <v>133752701</v>
       </c>
       <c r="B59" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638326</v>
+        <v>639153</v>
       </c>
       <c r="R59" t="n">
-        <v>7033938</v>
+        <v>7033912</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6428,7 +6428,7 @@
         <v>133752378</v>
       </c>
       <c r="B60" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B61" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R61" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6619,32 +6619,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133747965</v>
+        <v>133754273</v>
       </c>
       <c r="B62" t="n">
-        <v>91910</v>
+        <v>92389</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638071</v>
+        <v>638763</v>
       </c>
       <c r="R62" t="n">
-        <v>7034053</v>
+        <v>7033932</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6719,7 +6719,7 @@
         <v>133750648</v>
       </c>
       <c r="B63" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>133750259</v>
       </c>
       <c r="B64" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133754273</v>
+        <v>133747965</v>
       </c>
       <c r="B65" t="n">
-        <v>92379</v>
+        <v>91920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638763</v>
+        <v>638071</v>
       </c>
       <c r="R65" t="n">
-        <v>7033932</v>
+        <v>7034053</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7010,7 +7010,7 @@
         <v>133755120</v>
       </c>
       <c r="B66" t="n">
-        <v>92291</v>
+        <v>92301</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133754875</v>
+        <v>133754154</v>
       </c>
       <c r="B17" t="n">
-        <v>92349</v>
+        <v>92228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638759</v>
+        <v>638798</v>
       </c>
       <c r="R17" t="n">
-        <v>7033860</v>
+        <v>7033915</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133754154</v>
+        <v>133754875</v>
       </c>
       <c r="B18" t="n">
-        <v>92228</v>
+        <v>92349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6040186</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638798</v>
+        <v>638759</v>
       </c>
       <c r="R18" t="n">
-        <v>7033915</v>
+        <v>7033860</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2923,45 +2923,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133745623</v>
+        <v>133749592</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638018</v>
+        <v>638226</v>
       </c>
       <c r="R24" t="n">
-        <v>7034124</v>
+        <v>7034023</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3020,7 +3025,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133747740</v>
+        <v>133745623</v>
       </c>
       <c r="B25" t="n">
         <v>91957</v>
@@ -3051,14 +3056,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638064</v>
+        <v>638018</v>
       </c>
       <c r="R25" t="n">
-        <v>7034062</v>
+        <v>7034124</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,50 +3122,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133749592</v>
+        <v>133747740</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638226</v>
+        <v>638064</v>
       </c>
       <c r="R26" t="n">
-        <v>7034023</v>
+        <v>7034062</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133747269</v>
+        <v>133755234</v>
       </c>
       <c r="B29" t="n">
-        <v>80478</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,21 +3424,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638060</v>
+        <v>638761</v>
       </c>
       <c r="R29" t="n">
-        <v>7034027</v>
+        <v>7033856</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133755234</v>
+        <v>133747269</v>
       </c>
       <c r="B31" t="n">
-        <v>91920</v>
+        <v>80478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638761</v>
+        <v>638060</v>
       </c>
       <c r="R31" t="n">
-        <v>7033856</v>
+        <v>7034027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133751356</v>
+        <v>133750539</v>
       </c>
       <c r="B32" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638872</v>
+        <v>638536</v>
       </c>
       <c r="R32" t="n">
-        <v>7034031</v>
+        <v>7033920</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3801,32 +3801,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133750539</v>
+        <v>133751356</v>
       </c>
       <c r="B33" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638536</v>
+        <v>638872</v>
       </c>
       <c r="R33" t="n">
-        <v>7033920</v>
+        <v>7034031</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133754937</v>
+        <v>133750904</v>
       </c>
       <c r="B36" t="n">
         <v>91957</v>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638759</v>
+        <v>638620</v>
       </c>
       <c r="R36" t="n">
-        <v>7033864</v>
+        <v>7033897</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133750904</v>
+        <v>133754937</v>
       </c>
       <c r="B37" t="n">
         <v>91957</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638620</v>
+        <v>638759</v>
       </c>
       <c r="R37" t="n">
-        <v>7033897</v>
+        <v>7033864</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B38" t="n">
         <v>79358</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R38" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B39" t="n">
         <v>79358</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R39" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B40" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R40" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B41" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R41" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4771,50 +4771,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753992</v>
+        <v>133753051</v>
       </c>
       <c r="B43" t="n">
-        <v>57162</v>
+        <v>79358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638860</v>
+        <v>638997</v>
       </c>
       <c r="R43" t="n">
-        <v>7033902</v>
+        <v>7033854</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4873,32 +4868,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753051</v>
+        <v>133752438</v>
       </c>
       <c r="B44" t="n">
-        <v>79358</v>
+        <v>80477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638997</v>
+        <v>638928</v>
       </c>
       <c r="R44" t="n">
-        <v>7033854</v>
+        <v>7033996</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4970,10 +4965,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133752438</v>
+        <v>133753992</v>
       </c>
       <c r="B45" t="n">
-        <v>80477</v>
+        <v>57162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4981,34 +4976,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638928</v>
+        <v>638860</v>
       </c>
       <c r="R45" t="n">
-        <v>7033996</v>
+        <v>7033902</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133754841</v>
+        <v>133752847</v>
       </c>
       <c r="B47" t="n">
-        <v>92389</v>
+        <v>79358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638763</v>
+        <v>639087</v>
       </c>
       <c r="R47" t="n">
-        <v>7033857</v>
+        <v>7033883</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133752847</v>
+        <v>133755227</v>
       </c>
       <c r="B48" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>639087</v>
+        <v>638752</v>
       </c>
       <c r="R48" t="n">
-        <v>7033883</v>
+        <v>7033861</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133755227</v>
+        <v>133754841</v>
       </c>
       <c r="B49" t="n">
-        <v>91957</v>
+        <v>92389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638752</v>
+        <v>638763</v>
       </c>
       <c r="R49" t="n">
-        <v>7033861</v>
+        <v>7033857</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5649,45 +5649,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133745736</v>
+        <v>133752568</v>
       </c>
       <c r="B52" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>637993</v>
+        <v>639034</v>
       </c>
       <c r="R52" t="n">
-        <v>7034094</v>
+        <v>7034020</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133748447</v>
+        <v>133752413</v>
       </c>
       <c r="B53" t="n">
         <v>79358</v>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638162</v>
+        <v>638923</v>
       </c>
       <c r="R53" t="n">
-        <v>7034014</v>
+        <v>7034016</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133752568</v>
+        <v>133748447</v>
       </c>
       <c r="B54" t="n">
         <v>79358</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639034</v>
+        <v>638162</v>
       </c>
       <c r="R54" t="n">
-        <v>7034020</v>
+        <v>7034014</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133752413</v>
+        <v>133745736</v>
       </c>
       <c r="B55" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638923</v>
+        <v>637993</v>
       </c>
       <c r="R55" t="n">
-        <v>7034016</v>
+        <v>7034094</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133750078</v>
+        <v>133752304</v>
       </c>
       <c r="B57" t="n">
         <v>79358</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638351</v>
+        <v>638897</v>
       </c>
       <c r="R57" t="n">
-        <v>7033867</v>
+        <v>7034043</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133752304</v>
+        <v>133750078</v>
       </c>
       <c r="B58" t="n">
         <v>79358</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638897</v>
+        <v>638351</v>
       </c>
       <c r="R58" t="n">
-        <v>7034043</v>
+        <v>7033867</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B59" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R59" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133749947</v>
+        <v>133752701</v>
       </c>
       <c r="B61" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638326</v>
+        <v>639153</v>
       </c>
       <c r="R61" t="n">
-        <v>7033938</v>
+        <v>7033912</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6619,32 +6619,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133754273</v>
+        <v>133747965</v>
       </c>
       <c r="B62" t="n">
-        <v>92389</v>
+        <v>91920</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638763</v>
+        <v>638071</v>
       </c>
       <c r="R62" t="n">
-        <v>7033932</v>
+        <v>7034053</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133750648</v>
+        <v>133750259</v>
       </c>
       <c r="B63" t="n">
         <v>79358</v>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638588</v>
+        <v>638396</v>
       </c>
       <c r="R63" t="n">
-        <v>7033862</v>
+        <v>7033893</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133750259</v>
+        <v>133750648</v>
       </c>
       <c r="B64" t="n">
         <v>79358</v>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638396</v>
+        <v>638588</v>
       </c>
       <c r="R64" t="n">
-        <v>7033893</v>
+        <v>7033862</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133747965</v>
+        <v>133754273</v>
       </c>
       <c r="B65" t="n">
-        <v>91920</v>
+        <v>92389</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638071</v>
+        <v>638763</v>
       </c>
       <c r="R65" t="n">
-        <v>7034053</v>
+        <v>7033932</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133751145</v>
+        <v>133748002</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638754</v>
+        <v>638084</v>
       </c>
       <c r="R14" t="n">
-        <v>7033961</v>
+        <v>7034064</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133748002</v>
+        <v>133747890</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>92349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638084</v>
+        <v>638059</v>
       </c>
       <c r="R15" t="n">
-        <v>7034064</v>
+        <v>7034046</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133747890</v>
+        <v>133751145</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638059</v>
+        <v>638754</v>
       </c>
       <c r="R16" t="n">
-        <v>7034046</v>
+        <v>7033961</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133754154</v>
+        <v>133747219</v>
       </c>
       <c r="B17" t="n">
-        <v>92228</v>
+        <v>80473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638798</v>
+        <v>638061</v>
       </c>
       <c r="R17" t="n">
-        <v>7033915</v>
+        <v>7034028</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133747219</v>
+        <v>133754154</v>
       </c>
       <c r="B19" t="n">
-        <v>80473</v>
+        <v>92228</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638061</v>
+        <v>638798</v>
       </c>
       <c r="R19" t="n">
-        <v>7034028</v>
+        <v>7033915</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2923,50 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133749592</v>
+        <v>133747740</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638226</v>
+        <v>638064</v>
       </c>
       <c r="R24" t="n">
-        <v>7034023</v>
+        <v>7034062</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3025,45 +3020,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133745623</v>
+        <v>133749592</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638018</v>
+        <v>638226</v>
       </c>
       <c r="R25" t="n">
-        <v>7034124</v>
+        <v>7034023</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133747740</v>
+        <v>133745623</v>
       </c>
       <c r="B26" t="n">
         <v>91957</v>
@@ -3153,14 +3153,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638064</v>
+        <v>638018</v>
       </c>
       <c r="R26" t="n">
-        <v>7034062</v>
+        <v>7034124</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R28" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133755234</v>
+        <v>133747269</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>80478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,21 +3424,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638761</v>
+        <v>638060</v>
       </c>
       <c r="R29" t="n">
-        <v>7033856</v>
+        <v>7034027</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133747269</v>
+        <v>133755234</v>
       </c>
       <c r="B31" t="n">
-        <v>80478</v>
+        <v>91920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,21 +3618,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638060</v>
+        <v>638761</v>
       </c>
       <c r="R31" t="n">
-        <v>7034027</v>
+        <v>7033856</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133750539</v>
+        <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638536</v>
+        <v>638872</v>
       </c>
       <c r="R32" t="n">
-        <v>7033920</v>
+        <v>7034031</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3801,32 +3801,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133751356</v>
+        <v>133750539</v>
       </c>
       <c r="B33" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638872</v>
+        <v>638536</v>
       </c>
       <c r="R33" t="n">
-        <v>7034031</v>
+        <v>7033920</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133750904</v>
+        <v>133754937</v>
       </c>
       <c r="B36" t="n">
         <v>91957</v>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638620</v>
+        <v>638759</v>
       </c>
       <c r="R36" t="n">
-        <v>7033897</v>
+        <v>7033864</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133754937</v>
+        <v>133750904</v>
       </c>
       <c r="B37" t="n">
         <v>91957</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638759</v>
+        <v>638620</v>
       </c>
       <c r="R37" t="n">
-        <v>7033864</v>
+        <v>7033897</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4771,45 +4771,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753051</v>
+        <v>133753992</v>
       </c>
       <c r="B43" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638997</v>
+        <v>638860</v>
       </c>
       <c r="R43" t="n">
-        <v>7033854</v>
+        <v>7033902</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4868,32 +4873,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133752438</v>
+        <v>133753051</v>
       </c>
       <c r="B44" t="n">
-        <v>80477</v>
+        <v>79358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638928</v>
+        <v>638997</v>
       </c>
       <c r="R44" t="n">
-        <v>7033996</v>
+        <v>7033854</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4965,10 +4970,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133753992</v>
+        <v>133752438</v>
       </c>
       <c r="B45" t="n">
-        <v>57162</v>
+        <v>80477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4976,39 +4981,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638860</v>
+        <v>638928</v>
       </c>
       <c r="R45" t="n">
-        <v>7033902</v>
+        <v>7033996</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5164,32 +5164,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133752847</v>
+        <v>133754841</v>
       </c>
       <c r="B47" t="n">
-        <v>79358</v>
+        <v>92389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>639087</v>
+        <v>638763</v>
       </c>
       <c r="R47" t="n">
-        <v>7033883</v>
+        <v>7033857</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133755227</v>
+        <v>133752847</v>
       </c>
       <c r="B48" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,21 +5272,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638752</v>
+        <v>639087</v>
       </c>
       <c r="R48" t="n">
-        <v>7033861</v>
+        <v>7033883</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5358,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133754841</v>
+        <v>133755227</v>
       </c>
       <c r="B49" t="n">
-        <v>92389</v>
+        <v>91957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638763</v>
+        <v>638752</v>
       </c>
       <c r="R49" t="n">
-        <v>7033857</v>
+        <v>7033861</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133752568</v>
+        <v>133748447</v>
       </c>
       <c r="B52" t="n">
         <v>79358</v>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>639034</v>
+        <v>638162</v>
       </c>
       <c r="R52" t="n">
-        <v>7034020</v>
+        <v>7034014</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,45 +5746,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133752413</v>
+        <v>133745736</v>
       </c>
       <c r="B53" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638923</v>
+        <v>637993</v>
       </c>
       <c r="R53" t="n">
-        <v>7034016</v>
+        <v>7034094</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133748447</v>
+        <v>133752568</v>
       </c>
       <c r="B54" t="n">
         <v>79358</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638162</v>
+        <v>639034</v>
       </c>
       <c r="R54" t="n">
-        <v>7034014</v>
+        <v>7034020</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133745736</v>
+        <v>133752413</v>
       </c>
       <c r="B55" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>637993</v>
+        <v>638923</v>
       </c>
       <c r="R55" t="n">
-        <v>7034094</v>
+        <v>7034016</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133752304</v>
+        <v>133750078</v>
       </c>
       <c r="B57" t="n">
         <v>79358</v>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638897</v>
+        <v>638351</v>
       </c>
       <c r="R57" t="n">
-        <v>7034043</v>
+        <v>7033867</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133750078</v>
+        <v>133752304</v>
       </c>
       <c r="B58" t="n">
         <v>79358</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638351</v>
+        <v>638897</v>
       </c>
       <c r="R58" t="n">
-        <v>7033867</v>
+        <v>7034043</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133749947</v>
+        <v>133752701</v>
       </c>
       <c r="B59" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638326</v>
+        <v>639153</v>
       </c>
       <c r="R59" t="n">
-        <v>7033938</v>
+        <v>7033912</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B61" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R61" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6619,32 +6619,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133747965</v>
+        <v>133754273</v>
       </c>
       <c r="B62" t="n">
-        <v>91920</v>
+        <v>92389</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638071</v>
+        <v>638763</v>
       </c>
       <c r="R62" t="n">
-        <v>7034053</v>
+        <v>7033932</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133750259</v>
+        <v>133750648</v>
       </c>
       <c r="B63" t="n">
         <v>79358</v>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638396</v>
+        <v>638588</v>
       </c>
       <c r="R63" t="n">
-        <v>7033893</v>
+        <v>7033862</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133750648</v>
+        <v>133750259</v>
       </c>
       <c r="B64" t="n">
         <v>79358</v>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638588</v>
+        <v>638396</v>
       </c>
       <c r="R64" t="n">
-        <v>7033862</v>
+        <v>7033893</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133754273</v>
+        <v>133747965</v>
       </c>
       <c r="B65" t="n">
-        <v>92389</v>
+        <v>91920</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638763</v>
+        <v>638071</v>
       </c>
       <c r="R65" t="n">
-        <v>7033932</v>
+        <v>7034053</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133747219</v>
+        <v>133754875</v>
       </c>
       <c r="B17" t="n">
-        <v>80473</v>
+        <v>92349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638061</v>
+        <v>638759</v>
       </c>
       <c r="R17" t="n">
-        <v>7034028</v>
+        <v>7033860</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133754875</v>
+        <v>133754154</v>
       </c>
       <c r="B18" t="n">
-        <v>92349</v>
+        <v>92228</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638759</v>
+        <v>638798</v>
       </c>
       <c r="R18" t="n">
-        <v>7033860</v>
+        <v>7033915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133754154</v>
+        <v>133747219</v>
       </c>
       <c r="B19" t="n">
-        <v>92228</v>
+        <v>80473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638798</v>
+        <v>638061</v>
       </c>
       <c r="R19" t="n">
-        <v>7033915</v>
+        <v>7034028</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3413,10 +3413,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133747269</v>
+        <v>133755234</v>
       </c>
       <c r="B29" t="n">
-        <v>80478</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,21 +3424,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638060</v>
+        <v>638761</v>
       </c>
       <c r="R29" t="n">
-        <v>7034027</v>
+        <v>7033856</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3510,45 +3510,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133745777</v>
+        <v>133747269</v>
       </c>
       <c r="B30" t="n">
-        <v>92228</v>
+        <v>80478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638007</v>
+        <v>638060</v>
       </c>
       <c r="R30" t="n">
-        <v>7034104</v>
+        <v>7034027</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3607,45 +3607,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133755234</v>
+        <v>133745777</v>
       </c>
       <c r="B31" t="n">
-        <v>91920</v>
+        <v>92228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638761</v>
+        <v>638007</v>
       </c>
       <c r="R31" t="n">
-        <v>7033856</v>
+        <v>7034104</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B38" t="n">
         <v>79358</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R38" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B39" t="n">
         <v>79358</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R39" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R14" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133747890</v>
+        <v>133748002</v>
       </c>
       <c r="B15" t="n">
-        <v>92349</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638059</v>
+        <v>638084</v>
       </c>
       <c r="R15" t="n">
-        <v>7034046</v>
+        <v>7034064</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>92349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R16" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B27" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R27" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B28" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R28" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B38" t="n">
         <v>79358</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R38" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B39" t="n">
         <v>79358</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R39" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133751145</v>
+        <v>133748002</v>
       </c>
       <c r="B14" t="n">
         <v>79358</v>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638754</v>
+        <v>638084</v>
       </c>
       <c r="R14" t="n">
-        <v>7033961</v>
+        <v>7034064</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133748002</v>
+        <v>133747890</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>92349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638084</v>
+        <v>638059</v>
       </c>
       <c r="R15" t="n">
-        <v>7034064</v>
+        <v>7034046</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133747890</v>
+        <v>133751145</v>
       </c>
       <c r="B16" t="n">
-        <v>92349</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638059</v>
+        <v>638754</v>
       </c>
       <c r="R16" t="n">
-        <v>7034046</v>
+        <v>7033961</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3219,32 +3219,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133752723</v>
+        <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>639153</v>
+        <v>638131</v>
       </c>
       <c r="R27" t="n">
-        <v>7033913</v>
+        <v>7034032</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133748271</v>
+        <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638131</v>
+        <v>639153</v>
       </c>
       <c r="R28" t="n">
-        <v>7034032</v>
+        <v>7033913</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133752639</v>
+        <v>133748793</v>
       </c>
       <c r="B38" t="n">
         <v>79358</v>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>639103</v>
+        <v>638181</v>
       </c>
       <c r="R38" t="n">
-        <v>7033979</v>
+        <v>7034067</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133748793</v>
+        <v>133752639</v>
       </c>
       <c r="B39" t="n">
         <v>79358</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638181</v>
+        <v>639103</v>
       </c>
       <c r="R39" t="n">
-        <v>7034067</v>
+        <v>7033979</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1859,7 +1859,7 @@
         <v>133748644</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R14" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133747890</v>
+        <v>133748002</v>
       </c>
       <c r="B15" t="n">
-        <v>92349</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638059</v>
+        <v>638084</v>
       </c>
       <c r="R15" t="n">
-        <v>7034046</v>
+        <v>7034064</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>92351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R16" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2247,7 +2247,7 @@
         <v>133754875</v>
       </c>
       <c r="B17" t="n">
-        <v>92349</v>
+        <v>92351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>133754154</v>
       </c>
       <c r="B18" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>133747219</v>
       </c>
       <c r="B19" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>133745580</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,32 +2632,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133749740</v>
+        <v>133750092</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>92230</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638232</v>
+        <v>638348</v>
       </c>
       <c r="R21" t="n">
-        <v>7034015</v>
+        <v>7033866</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133750092</v>
+        <v>133749740</v>
       </c>
       <c r="B22" t="n">
-        <v>92228</v>
+        <v>91922</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638348</v>
+        <v>638232</v>
       </c>
       <c r="R22" t="n">
-        <v>7033866</v>
+        <v>7034015</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2829,7 +2829,7 @@
         <v>133754254</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>133747740</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>133745623</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>133748271</v>
       </c>
       <c r="B27" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>133752723</v>
       </c>
       <c r="B28" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>133755234</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>133747269</v>
       </c>
       <c r="B30" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>133745777</v>
       </c>
       <c r="B31" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>133751356</v>
       </c>
       <c r="B32" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>133750539</v>
       </c>
       <c r="B33" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133748499</v>
+        <v>133751033</v>
       </c>
       <c r="B34" t="n">
-        <v>91920</v>
+        <v>98051</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638163</v>
+        <v>638655</v>
       </c>
       <c r="R34" t="n">
-        <v>7034015</v>
+        <v>7033936</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133751033</v>
+        <v>133748499</v>
       </c>
       <c r="B35" t="n">
-        <v>98049</v>
+        <v>91922</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638655</v>
+        <v>638163</v>
       </c>
       <c r="R35" t="n">
-        <v>7033936</v>
+        <v>7034015</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4095,7 +4095,7 @@
         <v>133754937</v>
       </c>
       <c r="B36" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>133750904</v>
       </c>
       <c r="B37" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>133748793</v>
       </c>
       <c r="B38" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>133752639</v>
       </c>
       <c r="B39" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>133749803</v>
       </c>
       <c r="B40" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>133754117</v>
       </c>
       <c r="B41" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4674,45 +4674,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133747733</v>
+        <v>133753992</v>
       </c>
       <c r="B42" t="n">
-        <v>92672</v>
+        <v>57162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>898</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638052</v>
+        <v>638860</v>
       </c>
       <c r="R42" t="n">
-        <v>7034053</v>
+        <v>7033902</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4771,50 +4776,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133753992</v>
+        <v>133753051</v>
       </c>
       <c r="B43" t="n">
-        <v>57162</v>
+        <v>79359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638860</v>
+        <v>638997</v>
       </c>
       <c r="R43" t="n">
-        <v>7033902</v>
+        <v>7033854</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4873,32 +4873,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133753051</v>
+        <v>133752438</v>
       </c>
       <c r="B44" t="n">
-        <v>79358</v>
+        <v>80478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638997</v>
+        <v>638928</v>
       </c>
       <c r="R44" t="n">
-        <v>7033854</v>
+        <v>7033996</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4970,32 +4970,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133752438</v>
+        <v>133747733</v>
       </c>
       <c r="B45" t="n">
-        <v>80477</v>
+        <v>92674</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638928</v>
+        <v>638052</v>
       </c>
       <c r="R45" t="n">
-        <v>7033996</v>
+        <v>7034053</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5070,7 +5070,7 @@
         <v>133752659</v>
       </c>
       <c r="B46" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>133754841</v>
       </c>
       <c r="B47" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>133752847</v>
       </c>
       <c r="B48" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>133755227</v>
       </c>
       <c r="B49" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133748929</v>
+        <v>133747834</v>
       </c>
       <c r="B50" t="n">
-        <v>89338</v>
+        <v>92230</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638198</v>
+        <v>638050</v>
       </c>
       <c r="R50" t="n">
-        <v>7034077</v>
+        <v>7034042</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133747834</v>
+        <v>133748929</v>
       </c>
       <c r="B51" t="n">
-        <v>92228</v>
+        <v>89339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638050</v>
+        <v>638198</v>
       </c>
       <c r="R51" t="n">
-        <v>7034042</v>
+        <v>7034077</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5649,10 +5649,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133748447</v>
+        <v>133752568</v>
       </c>
       <c r="B52" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638162</v>
+        <v>639034</v>
       </c>
       <c r="R52" t="n">
-        <v>7034014</v>
+        <v>7034020</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5746,45 +5746,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133745736</v>
+        <v>133752413</v>
       </c>
       <c r="B53" t="n">
-        <v>91920</v>
+        <v>79359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>637993</v>
+        <v>638923</v>
       </c>
       <c r="R53" t="n">
-        <v>7034094</v>
+        <v>7034016</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133752568</v>
+        <v>133748447</v>
       </c>
       <c r="B54" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>639034</v>
+        <v>638162</v>
       </c>
       <c r="R54" t="n">
-        <v>7034020</v>
+        <v>7034014</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5940,45 +5940,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133752413</v>
+        <v>133745736</v>
       </c>
       <c r="B55" t="n">
-        <v>79358</v>
+        <v>91922</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638923</v>
+        <v>637993</v>
       </c>
       <c r="R55" t="n">
-        <v>7034016</v>
+        <v>7034094</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6040,7 +6040,7 @@
         <v>133751279</v>
       </c>
       <c r="B56" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>133750078</v>
       </c>
       <c r="B57" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>133752304</v>
       </c>
       <c r="B58" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133752701</v>
+        <v>133749947</v>
       </c>
       <c r="B59" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,21 +6339,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>639153</v>
+        <v>638326</v>
       </c>
       <c r="R59" t="n">
-        <v>7033912</v>
+        <v>7033938</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6425,10 +6425,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133752378</v>
+        <v>133752701</v>
       </c>
       <c r="B60" t="n">
-        <v>89338</v>
+        <v>79359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,21 +6436,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638902</v>
+        <v>639153</v>
       </c>
       <c r="R60" t="n">
-        <v>7034025</v>
+        <v>7033912</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133749947</v>
+        <v>133752378</v>
       </c>
       <c r="B61" t="n">
-        <v>91957</v>
+        <v>89339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6533,21 +6533,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638326</v>
+        <v>638902</v>
       </c>
       <c r="R61" t="n">
-        <v>7033938</v>
+        <v>7034025</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6622,7 +6622,7 @@
         <v>133754273</v>
       </c>
       <c r="B62" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>133750648</v>
       </c>
       <c r="B63" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>133750259</v>
       </c>
       <c r="B64" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>133747965</v>
       </c>
       <c r="B65" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>133755120</v>
       </c>
       <c r="B66" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133751145</v>
+        <v>133747890</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>92351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638754</v>
+        <v>638059</v>
       </c>
       <c r="R14" t="n">
-        <v>7033961</v>
+        <v>7034046</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133748002</v>
+        <v>133751145</v>
       </c>
       <c r="B15" t="n">
         <v>79359</v>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638084</v>
+        <v>638754</v>
       </c>
       <c r="R15" t="n">
-        <v>7034064</v>
+        <v>7033961</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133747890</v>
+        <v>133748002</v>
       </c>
       <c r="B16" t="n">
-        <v>92351</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638059</v>
+        <v>638084</v>
       </c>
       <c r="R16" t="n">
-        <v>7034046</v>
+        <v>7034064</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133754875</v>
+        <v>133747219</v>
       </c>
       <c r="B17" t="n">
-        <v>92351</v>
+        <v>80474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638759</v>
+        <v>638061</v>
       </c>
       <c r="R17" t="n">
-        <v>7033860</v>
+        <v>7034028</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133754154</v>
+        <v>133745580</v>
       </c>
       <c r="B18" t="n">
-        <v>92230</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,34 +2352,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Ång</t>
+          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638798</v>
+        <v>637989</v>
       </c>
       <c r="R18" t="n">
-        <v>7033915</v>
+        <v>7034113</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133747219</v>
+        <v>133754875</v>
       </c>
       <c r="B19" t="n">
-        <v>80474</v>
+        <v>92351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638061</v>
+        <v>638759</v>
       </c>
       <c r="R19" t="n">
-        <v>7034028</v>
+        <v>7033860</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133745580</v>
+        <v>133754154</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>92230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,34 +2546,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Södra Bergvattnet, Södra Bergvattnet, Ång</t>
+          <t>Stormyran, Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637989</v>
+        <v>638798</v>
       </c>
       <c r="R20" t="n">
-        <v>7034113</v>
+        <v>7033915</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133749803</v>
+        <v>133754117</v>
       </c>
       <c r="B40" t="n">
-        <v>91959</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638278</v>
+        <v>638808</v>
       </c>
       <c r="R40" t="n">
-        <v>7033979</v>
+        <v>7033918</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4577,10 +4577,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133754117</v>
+        <v>133749803</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>91959</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4588,21 +4588,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638808</v>
+        <v>638278</v>
       </c>
       <c r="R41" t="n">
-        <v>7033918</v>
+        <v>7033979</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133747834</v>
+        <v>133748929</v>
       </c>
       <c r="B50" t="n">
-        <v>92230</v>
+        <v>89339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638050</v>
+        <v>638198</v>
       </c>
       <c r="R50" t="n">
-        <v>7034042</v>
+        <v>7034077</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133748929</v>
+        <v>133747834</v>
       </c>
       <c r="B51" t="n">
-        <v>89339</v>
+        <v>92230</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638198</v>
+        <v>638050</v>
       </c>
       <c r="R51" t="n">
-        <v>7034077</v>
+        <v>7034042</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>

--- a/artfynd/A 21985-2026 artfynd.xlsx
+++ b/artfynd/A 21985-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133751927</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752378</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133745777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747834</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750092</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754154</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747733</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712677</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712769</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133745623</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133746520</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747740</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133749803</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133749947</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750904</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2334,6 +2419,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754254</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2431,6 +2521,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754937</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2528,6 +2623,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755227</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2629,6 +2729,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712771</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736931</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2827,6 +2937,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752183</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2924,6 +3039,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754273</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3021,6 +3141,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754841</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3120,6 +3245,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712679</t>
         </is>
       </c>
     </row>
@@ -3223,6 +3353,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755120</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3320,6 +3455,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757073</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3417,6 +3557,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133745736</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3514,6 +3659,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133746610</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3611,6 +3761,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747965</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3708,6 +3863,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748499</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3805,6 +3965,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133749740</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3902,6 +4067,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133751356</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3999,6 +4169,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752659</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4096,6 +4271,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752723</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4193,6 +4373,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755234</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4294,6 +4479,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712774</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4400,6 +4590,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712675</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4506,6 +4701,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712773</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4603,6 +4803,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133745580</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4700,6 +4905,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748002</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4797,6 +5007,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748271</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4894,6 +5109,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748447</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4991,6 +5211,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748644</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5088,6 +5313,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748793</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5185,6 +5415,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750078</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5282,6 +5517,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750259</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5379,6 +5619,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750539</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5476,6 +5721,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133750648</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5573,6 +5823,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133751145</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5670,6 +5925,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133751279</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5767,6 +6027,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752304</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5864,6 +6129,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752413</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5961,6 +6231,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752494</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6058,6 +6333,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752568</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6155,6 +6435,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752639</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6252,6 +6537,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752701</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6349,6 +6639,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752847</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6446,6 +6741,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133753051</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6543,6 +6843,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754117</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6640,6 +6945,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755472</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6741,6 +7051,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712674</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6847,6 +7162,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712678</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6948,6 +7268,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738071</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7045,6 +7370,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133745367</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7142,6 +7472,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747219</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7239,6 +7574,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752438</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7336,6 +7676,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747269</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7442,6 +7787,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712676</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7544,6 +7894,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748818</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7646,6 +8001,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133752280</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7752,6 +8112,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712758</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7859,6 +8224,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133746414</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7966,6 +8336,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133748711</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8073,6 +8448,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133755347</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8179,6 +8559,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712770</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8281,6 +8666,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133749592</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8383,6 +8773,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133753992</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8489,6 +8884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712767</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8590,6 +8990,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747399</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8687,6 +9092,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133751033</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8788,6 +9198,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712772</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8885,6 +9300,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133747890</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8982,8 +9402,99 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133754875</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>